--- a/output/stock_quant_scores/INTU_balance_df.xlsx
+++ b/output/stock_quant_scores/INTU_balance_df.xlsx
@@ -1853,25 +1853,35 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>7540000000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>1417000000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>16441000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>13581000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>11293000000</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1887,7 +1897,9 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>3630000000</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1912,7 +1924,9 @@
         <v>3000000</v>
       </c>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>27734000000</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1931,7 +1945,9 @@
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>5047000000</v>
+      </c>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="n">
@@ -1949,7 +1965,9 @@
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
+      <c r="CG6" t="n">
+        <v>2796000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
